--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.43225653206654</v>
+        <v>2.182741686460812</v>
       </c>
       <c r="D2" t="n">
-        <v>16.07984464785823</v>
+        <v>2.612974755276963</v>
       </c>
       <c r="E2" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F2" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.9205201412235</v>
+        <v>2.587084522948819</v>
       </c>
       <c r="D3" t="n">
-        <v>14.36215878405022</v>
+        <v>2.333850802408161</v>
       </c>
       <c r="E3" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F3" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7864045016758</v>
+        <v>8.902790731522318</v>
       </c>
       <c r="D4" t="n">
-        <v>22.75401438969665</v>
+        <v>3.697527338325705</v>
       </c>
       <c r="E4" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F4" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.01657392575508</v>
+        <v>8.452693262935201</v>
       </c>
       <c r="D5" t="n">
-        <v>23.99048854449644</v>
+        <v>3.898454388480672</v>
       </c>
       <c r="E5" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F5" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.17893997138603</v>
+        <v>3.441577745350231</v>
       </c>
       <c r="D6" t="n">
-        <v>19.83587399294428</v>
+        <v>3.223329523853446</v>
       </c>
       <c r="E6" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F6" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.70701066263905</v>
+        <v>2.064889232678845</v>
       </c>
       <c r="D7" t="n">
-        <v>12.44282280640048</v>
+        <v>2.021958706040078</v>
       </c>
       <c r="E7" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F7" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.57993394808097</v>
+        <v>3.019239266563157</v>
       </c>
       <c r="D8" t="n">
-        <v>21.52361197007234</v>
+        <v>3.497586945136756</v>
       </c>
       <c r="E8" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F8" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.83102175023216</v>
+        <v>4.197541034412727</v>
       </c>
       <c r="D9" t="n">
-        <v>28.47971748353613</v>
+        <v>4.627954091074621</v>
       </c>
       <c r="E9" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F9" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28836742377309</v>
+        <v>6.384359706363127</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75197912935516</v>
+        <v>4.672196608520214</v>
       </c>
       <c r="E10" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F10" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.46909682843614</v>
+        <v>6.088728234620874</v>
       </c>
       <c r="D11" t="n">
-        <v>21.1482859825566</v>
+        <v>3.436596472165448</v>
       </c>
       <c r="E11" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F11" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49848779634149</v>
+        <v>5.606004266905493</v>
       </c>
       <c r="D12" t="n">
-        <v>22.20923231451281</v>
+        <v>3.609000251108332</v>
       </c>
       <c r="E12" t="n">
-        <v>14.32447844018282</v>
+        <v>2.327727746529708</v>
       </c>
       <c r="F12" t="n">
-        <v>4.978465484991857</v>
+        <v>0.8090006413111767</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
